--- a/bitacora/valores_entrada.xlsx
+++ b/bitacora/valores_entrada.xlsx
@@ -5,19 +5,31 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prog\indicadores_enoe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Prog\indicadores_enoe\bitacora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45027C3B-9D17-4BF2-B479-61D55339259F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B694478-4E44-4357-848E-80A9775AE52F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="3" xr2:uid="{788508E7-8DF0-4771-9409-F8AEF21F5EA4}"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" activeTab="8" xr2:uid="{788508E7-8DF0-4771-9409-F8AEF21F5EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
     <sheet name="desagregado" sheetId="2" r:id="rId2"/>
     <sheet name="pob_tot" sheetId="3" r:id="rId3"/>
     <sheet name="pob_sub" sheetId="4" r:id="rId4"/>
+    <sheet name="valores" sheetId="6" r:id="rId5"/>
+    <sheet name="valores (2)" sheetId="7" r:id="rId6"/>
+    <sheet name="cuadro" sheetId="8" r:id="rId7"/>
+    <sheet name="contraste" sheetId="9" r:id="rId8"/>
+    <sheet name="Hoja2" sheetId="10" r:id="rId9"/>
+    <sheet name="cve_ent" sheetId="11" r:id="rId10"/>
+    <sheet name="Hoja1" sheetId="12" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">contraste!$A$1:$A$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">cuadro!$A$1:$A$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Hoja2!$B$1:$F$41</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="337">
   <si>
     <t xml:space="preserve">~nombre, </t>
   </si>
@@ -75,15 +87,9 @@
     <t xml:space="preserve">"topd", </t>
   </si>
   <si>
-    <t xml:space="preserve">"clase2 == 2 &amp; dur9c == 2", </t>
-  </si>
-  <si>
     <t xml:space="preserve">"tpg", </t>
   </si>
   <si>
-    <t xml:space="preserve">"clase2 == 2 &amp; tpg_p8a == 1", </t>
-  </si>
-  <si>
     <t xml:space="preserve">"tta", </t>
   </si>
   <si>
@@ -189,214 +195,874 @@
     <t xml:space="preserve">~datos, ~poblacion, ~filtro, </t>
   </si>
   <si>
-    <t xml:space="preserve">"sdem", "pea", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pnea", "clase1 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "ocupada", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "desocupada", "clase2 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "disponible", "clase2 == 3", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "no disponible", "clase2 == 4", </t>
-  </si>
-  <si>
     <t xml:space="preserve">~datos, ~nombre, ~filtro_num, ~filtro_den, </t>
   </si>
   <si>
-    <t xml:space="preserve">"sdem", "tp", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "td", "clase2 == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "topd", "clase2 == 2 &amp; dur9c == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tpg", "clase2 == 2 &amp; tpg_p8a == 1", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tta", "remune2c == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tsub", "sub_o == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tcco", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi1", "tue2 == 5", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til1", "emp_ppal == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi2", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til2", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
     <t xml:space="preserve">~datos, ~nombre, ~grupo, ~filtro_num, ~filtro_den, </t>
   </si>
   <si>
-    <t xml:space="preserve">"sdem", "tp", "sex", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "td", "sex", "clase2 == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "topd", "sex", "clase2 == 2 | dur9c == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tpg", "sex", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tta", "sex", "remune2c == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tsub", "sex", "sub_o == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tcco", "sex", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi1", "sex", "tue2 == 5", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til1", "sex", "emp_ppal == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi2", "sex", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til2", "sex", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tp", "cve_ent", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "td", "cve_ent", "clase2 == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "topd", "cve_ent", "clase2 == 2 | dur9c == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tpg", "cve_ent", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tta", "cve_ent", "remune2c == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tsub", "cve_ent", "sub_o == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tcco", "cve_ent", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi1", "cve_ent", "tue2 == 5", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til1", "cve_ent", "emp_ppal == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi2", "cve_ent", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til2", "cve_ent", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tp", "cd_a", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "td", "cd_a", "clase2 == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "topd", "cd_a", "clase2 == 2 | dur9c == 2", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tpg", "cd_a", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tta", "cd_a", "remune2c == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tsub", "cd_a", "sub_o == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tcco", "cd_a", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi1", "cd_a", "tue2 == 5", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til1", "cd_a", "emp_ppal == 1", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "tosi2", "cd_a", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "til2", "cd_a", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pea", "sex", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pnea", "sex", "clase1 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "ocupada", "sex", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "desocupada", "sex", "clase2 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "disponible", "sex", "clase2 == 3", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "no disponible", "sex", "clase2 == 4", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pea", "cve_ent", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pnea", "cve_ent", "clase1 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "ocupada", "cve_ent", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "desocupada", "cve_ent", "clase2 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "disponible", "cve_ent", "clase2 == 3", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "no disponible", "cve_ent", "clase2 == 4", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pea", "cd_a", "clase1 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "pnea", "cd_a", "clase1 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "ocupada", "cd_a", "clase2 == 1", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "desocupada", "cd_a", "clase2 == 2", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "disponible", "cd_a", "clase2 == 3", </t>
-  </si>
-  <si>
-    <t xml:space="preserve">"sdem", "no disponible", "cd_a", "clase2 == 4", </t>
+    <t>",</t>
+  </si>
+  <si>
+    <t>" = "</t>
+  </si>
+  <si>
+    <t>Áreas rurales o comp. urb.</t>
+  </si>
+  <si>
+    <t>"</t>
+  </si>
+  <si>
+    <t>Áreas rurales hasta 86</t>
+  </si>
+  <si>
+    <t>Tapachula</t>
+  </si>
+  <si>
+    <t>Reynosa</t>
+  </si>
+  <si>
+    <t>Mexicali</t>
+  </si>
+  <si>
+    <t>Pachuca</t>
+  </si>
+  <si>
+    <t>Ciudad del Carmen</t>
+  </si>
+  <si>
+    <t>Cancún</t>
+  </si>
+  <si>
+    <t>La Paz</t>
+  </si>
+  <si>
+    <t>Tlaxcala</t>
+  </si>
+  <si>
+    <t>Querétaro</t>
+  </si>
+  <si>
+    <t>Colima</t>
+  </si>
+  <si>
+    <t>Zacatecas</t>
+  </si>
+  <si>
+    <t>Oaxaca</t>
+  </si>
+  <si>
+    <t>Coatzacoalcos</t>
+  </si>
+  <si>
+    <t>Cuernavaca</t>
+  </si>
+  <si>
+    <t>Campeche</t>
+  </si>
+  <si>
+    <t>Tepic</t>
+  </si>
+  <si>
+    <t>Durango</t>
+  </si>
+  <si>
+    <t>Hermosillo</t>
+  </si>
+  <si>
+    <t>Culiacán</t>
+  </si>
+  <si>
+    <t>Tijuana</t>
+  </si>
+  <si>
+    <t>Ciudad Juárez</t>
+  </si>
+  <si>
+    <t>Tuxtla Gutiérrez</t>
+  </si>
+  <si>
+    <t>Villahermosa</t>
+  </si>
+  <si>
+    <t>Saltillo</t>
+  </si>
+  <si>
+    <t>Toluca</t>
+  </si>
+  <si>
+    <t>Morelia</t>
+  </si>
+  <si>
+    <t>Aguascalientes</t>
+  </si>
+  <si>
+    <t>Acapulco</t>
+  </si>
+  <si>
+    <t>Veracruz</t>
+  </si>
+  <si>
+    <t>Tampico</t>
+  </si>
+  <si>
+    <t>Chihuahua</t>
+  </si>
+  <si>
+    <t>Mérida</t>
+  </si>
+  <si>
+    <t>San Luis Potosí</t>
+  </si>
+  <si>
+    <t>Torreón</t>
+  </si>
+  <si>
+    <t>León</t>
+  </si>
+  <si>
+    <t>Puebla</t>
+  </si>
+  <si>
+    <t>Monterrey</t>
+  </si>
+  <si>
+    <t>Guadalajara</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
+    <t>Tapachula (Chis.)</t>
+  </si>
+  <si>
+    <t>Reynosa (Tamps.)</t>
+  </si>
+  <si>
+    <t>Mexicali (B. C.)</t>
+  </si>
+  <si>
+    <t>Pachuca (Hgo.)</t>
+  </si>
+  <si>
+    <t>Ciudad del Carmen (Camp.)</t>
+  </si>
+  <si>
+    <t>Cancún (Q. Roo)</t>
+  </si>
+  <si>
+    <t>La Paz (B. C. S.)</t>
+  </si>
+  <si>
+    <t>Tlaxcala (Tlax.)</t>
+  </si>
+  <si>
+    <t>Querétaro (Qro.)</t>
+  </si>
+  <si>
+    <t>Colima (Col.)</t>
+  </si>
+  <si>
+    <t>Zacatecas (Zac.)</t>
+  </si>
+  <si>
+    <t>Oaxaca (Oax.)</t>
+  </si>
+  <si>
+    <t>Coatzacoalcos (Ver.)</t>
+  </si>
+  <si>
+    <t>Cuernavaca (Mor.)</t>
+  </si>
+  <si>
+    <t>Campeche (Camp.)</t>
+  </si>
+  <si>
+    <t>Tepic (Nay.)</t>
+  </si>
+  <si>
+    <t>Durango (Dgo.)</t>
+  </si>
+  <si>
+    <t>Hermosillo (Son.)</t>
+  </si>
+  <si>
+    <t>Culiacán (Sin.)</t>
+  </si>
+  <si>
+    <t>Tijuana (B. C.)</t>
+  </si>
+  <si>
+    <t>Ciudad Juárez (Chih.)</t>
+  </si>
+  <si>
+    <t>Tuxtla Gutiérrez (Chis.)</t>
+  </si>
+  <si>
+    <t>Villahermosa (Tab.)</t>
+  </si>
+  <si>
+    <t>Saltillo (Coah.)</t>
+  </si>
+  <si>
+    <t>Toluca (Méx.)</t>
+  </si>
+  <si>
+    <t>Morelia (Mich.)</t>
+  </si>
+  <si>
+    <t>Aguascalientes (Ags.)</t>
+  </si>
+  <si>
+    <t>Acapulco de Juárez (Gro.)</t>
+  </si>
+  <si>
+    <t>Veracruz (Ver.)</t>
+  </si>
+  <si>
+    <t>Tampico (Tamps. y Ver.)</t>
+  </si>
+  <si>
+    <t>Chihuahua (Chih.)</t>
+  </si>
+  <si>
+    <t>Mérida (Yuc.)</t>
+  </si>
+  <si>
+    <t>San Luis Potosí (S. L. P.)</t>
+  </si>
+  <si>
+    <t>Torreón - La Laguna (Coah. y Dgo.)</t>
+  </si>
+  <si>
+    <t>León (Gto.)</t>
+  </si>
+  <si>
+    <t>Puebla (Pue.)</t>
+  </si>
+  <si>
+    <t>Monterrey (N. L.)</t>
+  </si>
+  <si>
+    <t>Guadalajara (Jal.)</t>
+  </si>
+  <si>
+    <t>Ciudad de México (CDMX y Méx.)</t>
+  </si>
+  <si>
+    <t>Categoría 2</t>
+  </si>
+  <si>
+    <t>Zacatecas (Zac.</t>
+  </si>
+  <si>
+    <t>Villahermosa (Tab.</t>
+  </si>
+  <si>
+    <t>Veracruz (Ver.</t>
+  </si>
+  <si>
+    <t>Tuxtla Gutiérrez (Chis.</t>
+  </si>
+  <si>
+    <t>Torreón - La Laguna (Coah. y Dgo.</t>
+  </si>
+  <si>
+    <t>Toluca (Méx.</t>
+  </si>
+  <si>
+    <t>Tlaxcala (Tlax.</t>
+  </si>
+  <si>
+    <t>Tijuana (B. C.</t>
+  </si>
+  <si>
+    <t>Tepic (Nay.</t>
+  </si>
+  <si>
+    <t>Tapachula (Chis.</t>
+  </si>
+  <si>
+    <t>Tampico (Tamps. y Ver.</t>
+  </si>
+  <si>
+    <t>San Luis Potosí (S. L. P.</t>
+  </si>
+  <si>
+    <t>Saltillo (Coah.</t>
+  </si>
+  <si>
+    <t>Reynosa (Tamps.</t>
+  </si>
+  <si>
+    <t>Querétaro (Qro.</t>
+  </si>
+  <si>
+    <t>Puebla (Pue.</t>
+  </si>
+  <si>
+    <t>Pachuca (Hgo.</t>
+  </si>
+  <si>
+    <t>Oaxaca (Oax.</t>
+  </si>
+  <si>
+    <t>Morelia (Mich.</t>
+  </si>
+  <si>
+    <t>Monterrey (N. L.</t>
+  </si>
+  <si>
+    <t>Mexicali (B. C.</t>
+  </si>
+  <si>
+    <t>Mérida (Yuc.</t>
+  </si>
+  <si>
+    <t>León (Gto.</t>
+  </si>
+  <si>
+    <t>La Paz (B. C. S.</t>
+  </si>
+  <si>
+    <t>Hermosillo (Son.</t>
+  </si>
+  <si>
+    <t>Guadalajara (Jal.</t>
+  </si>
+  <si>
+    <t>Durango (Dgo.</t>
+  </si>
+  <si>
+    <t>Culiacán (Sin.</t>
+  </si>
+  <si>
+    <t>Cuernavaca (Mor.</t>
+  </si>
+  <si>
+    <t>Colima (Col.</t>
+  </si>
+  <si>
+    <t>Coatzacoalcos (Ver.</t>
+  </si>
+  <si>
+    <t>Ciudad Juárez (Chih.</t>
+  </si>
+  <si>
+    <t>Ciudad del Carmen (Camp.</t>
+  </si>
+  <si>
+    <t>Ciudad de México (CDMX y Méx.</t>
+  </si>
+  <si>
+    <t>Chihuahua (Chih.</t>
+  </si>
+  <si>
+    <t>Cancún (Q. Roo</t>
+  </si>
+  <si>
+    <t>Campeche (Camp.</t>
+  </si>
+  <si>
+    <t>Aguascalientes (Ags.</t>
+  </si>
+  <si>
+    <t>Acapulco de Juárez (Gro.</t>
+  </si>
+  <si>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>cd_cuadro</t>
+  </si>
+  <si>
+    <t>cd_a_dic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"sdem_cd", </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acapulco de Juárez </t>
+  </si>
+  <si>
+    <t>Gro.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aguascalientes </t>
+  </si>
+  <si>
+    <t>Ags.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campeche </t>
+  </si>
+  <si>
+    <t>Camp.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancún </t>
+  </si>
+  <si>
+    <t>Q. Roo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chihuahua </t>
+  </si>
+  <si>
+    <t>Chih.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad del Carmen </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad Juárez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coatzacoalcos </t>
+  </si>
+  <si>
+    <t>Ver.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colima </t>
+  </si>
+  <si>
+    <t>Col.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuernavaca </t>
+  </si>
+  <si>
+    <t>Mor.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Culiacán </t>
+  </si>
+  <si>
+    <t>Sin.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durango </t>
+  </si>
+  <si>
+    <t>Dgo.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guadalajara </t>
+  </si>
+  <si>
+    <t>Jal.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hermosillo </t>
+  </si>
+  <si>
+    <t>Son.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Paz </t>
+  </si>
+  <si>
+    <t>B. C. S.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">León </t>
+  </si>
+  <si>
+    <t>Gto.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mérida </t>
+  </si>
+  <si>
+    <t>Yuc.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mexicali </t>
+  </si>
+  <si>
+    <t>B. C.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad de México </t>
+  </si>
+  <si>
+    <t>CDMX y Méx.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monterrey </t>
+  </si>
+  <si>
+    <t>N. L.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morelia </t>
+  </si>
+  <si>
+    <t>Mich.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oaxaca </t>
+  </si>
+  <si>
+    <t>Oax.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pachuca </t>
+  </si>
+  <si>
+    <t>Hgo.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puebla </t>
+  </si>
+  <si>
+    <t>Pue.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Querétaro </t>
+  </si>
+  <si>
+    <t>Qro.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reynosa </t>
+  </si>
+  <si>
+    <t>Tamps.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltillo </t>
+  </si>
+  <si>
+    <t>Coah.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Luis Potosí </t>
+  </si>
+  <si>
+    <t>S. L. P.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tampico </t>
+  </si>
+  <si>
+    <t>Tamps. y Ver.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tapachula </t>
+  </si>
+  <si>
+    <t>Chis.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tepic </t>
+  </si>
+  <si>
+    <t>Nay.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tijuana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tlaxcala </t>
+  </si>
+  <si>
+    <t>Tlax.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toluca </t>
+  </si>
+  <si>
+    <t>Méx.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torreón - La Laguna </t>
+  </si>
+  <si>
+    <t>Coah. y Dgo.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuxtla Gutiérrez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veracruz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villahermosa </t>
+  </si>
+  <si>
+    <t>Tab.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zacatecas </t>
+  </si>
+  <si>
+    <t>Zac.)</t>
+  </si>
+  <si>
+    <t>ABREV</t>
+  </si>
+  <si>
+    <t>CVE_ENT</t>
+  </si>
+  <si>
+    <t>NOM_ENT</t>
+  </si>
+  <si>
+    <t>NOM_ABR</t>
+  </si>
+  <si>
+    <t>AGS</t>
+  </si>
+  <si>
+    <t>Baja California</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>Baja California Sur</t>
+  </si>
+  <si>
+    <t>BCS</t>
+  </si>
+  <si>
+    <t>CAMP</t>
+  </si>
+  <si>
+    <t>Coahuila de Zaragoza</t>
+  </si>
+  <si>
+    <t>COAH</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>Chiapas</t>
+  </si>
+  <si>
+    <t>CHIS</t>
+  </si>
+  <si>
+    <t>CHIH</t>
+  </si>
+  <si>
+    <t>Ciudad de México</t>
+  </si>
+  <si>
+    <t>CDMX</t>
+  </si>
+  <si>
+    <t>DGO</t>
+  </si>
+  <si>
+    <t>Guanajuato</t>
+  </si>
+  <si>
+    <t>GTO</t>
+  </si>
+  <si>
+    <t>Guerrero</t>
+  </si>
+  <si>
+    <t>GRO</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>HGO</t>
+  </si>
+  <si>
+    <t>Jalisco</t>
+  </si>
+  <si>
+    <t>JAL</t>
+  </si>
+  <si>
+    <t>MÉX</t>
+  </si>
+  <si>
+    <t>Michoacán de Ocampo</t>
+  </si>
+  <si>
+    <t>MICH</t>
+  </si>
+  <si>
+    <t>Morelos</t>
+  </si>
+  <si>
+    <t>MOR</t>
+  </si>
+  <si>
+    <t>Nayarit</t>
+  </si>
+  <si>
+    <t>NAY</t>
+  </si>
+  <si>
+    <t>Nuevo León</t>
+  </si>
+  <si>
+    <t>NL</t>
+  </si>
+  <si>
+    <t>OAX</t>
+  </si>
+  <si>
+    <t>PUE</t>
+  </si>
+  <si>
+    <t>QRO</t>
+  </si>
+  <si>
+    <t>Quintana Roo</t>
+  </si>
+  <si>
+    <t>Q ROO</t>
+  </si>
+  <si>
+    <t>SLP</t>
+  </si>
+  <si>
+    <t>Sinaloa</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>Sonora</t>
+  </si>
+  <si>
+    <t>SON</t>
+  </si>
+  <si>
+    <t>Tabasco</t>
+  </si>
+  <si>
+    <t>TAB</t>
+  </si>
+  <si>
+    <t>Tamaulipas</t>
+  </si>
+  <si>
+    <t>TAMPS</t>
+  </si>
+  <si>
+    <t>TLAX</t>
+  </si>
+  <si>
+    <t>Veracruz de Ignacio de la Llave</t>
+  </si>
+  <si>
+    <t>VER</t>
+  </si>
+  <si>
+    <t>Yucatán</t>
+  </si>
+  <si>
+    <t>YUC</t>
+  </si>
+  <si>
+    <t>ZAC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tosi2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tp</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> td</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> topd</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tta</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tsub</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tcco</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> til1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tosi1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> til2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = "</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Participación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desocupación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación parcial y desocupación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presión general </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trabajo asalariado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subocupación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condiciones críticas de ocupación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informalidad laboral 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación en el sector informal 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informalidad laboral 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocupación en el sector informal 2 </t>
+  </si>
+  <si>
+    <t>(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">", </t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">, </t>
+  </si>
+  <si>
+    <t># ------</t>
+  </si>
+  <si>
+    <t>cve_ent</t>
   </si>
 </sst>
 </file>
@@ -412,12 +1078,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -432,8 +1104,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,10 +1423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E495755B-9F16-4070-8F76-AACDFDC8413F}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.21875" bestFit="1" customWidth="1"/>
@@ -771,15 +1446,15 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -795,8 +1470,9 @@
       <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" t="s">
-        <v>56</v>
+      <c r="F3" t="str">
+        <f>_xlfn.CONCAT(A3:D3)</f>
+        <v xml:space="preserve">"sdem", "tp", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -812,8 +1488,9 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" t="s">
-        <v>57</v>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4:F24" si="0">_xlfn.CONCAT(A4:D4)</f>
+        <v xml:space="preserve">"sdem", "td", "clase2 == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -824,13 +1501,14 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
-        <v>58</v>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "topd", "clase2 == 2 | dur9c == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -838,16 +1516,17 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
-        <v>59</v>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tpg", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -855,16 +1534,17 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tta", "remune2c == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -872,16 +1552,17 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
+        <v>14</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tsub", "sub_o == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -889,16 +1570,17 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
+        <v>14</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tcco", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -906,16 +1588,17 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
+        <v>14</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "til1", "emp_ppal == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -923,16 +1606,17 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
+        <v>14</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tosi1", "tue2 == 5", "clase2 == 1", </v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -940,16 +1624,17 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "til2", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -957,16 +1642,1451 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tosi2", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tp", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "td", "clase2 == 2", "clase1 == 1", </v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "topd", "clase2 == 2 | dur9c == 2", "clase1 == 1", </v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tpg", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tta", "remune2c == 1", "clase2 == 1", </v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tsub", "sub_o == 1", "clase2 == 1", </v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tcco", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "til1", "emp_ppal == 1", "clase2 == 1", </v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tosi1", "tue2 == 5", "clase2 == 1", </v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "til2", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tosi2", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AA02149-42A4-4B49-9C85-9EDBA19F655F}">
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" t="str">
+        <f>_xlfn.CONCAT(E2:J2)</f>
+        <v>"Aguascalientes" = "01",</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>2</v>
+      </c>
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L33" si="0">_xlfn.CONCAT(E3:J3)</f>
+        <v>"Baja California" = "02",</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
+        <v>258</v>
+      </c>
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>3</v>
+      </c>
+      <c r="J4" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="0"/>
+        <v>"Baja California Sur" = "03",</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>4</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="0"/>
+        <v>"Campeche" = "04",</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5</v>
+      </c>
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="0"/>
+        <v>"Coahuila de Zaragoza" = "05",</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>6</v>
+      </c>
+      <c r="J7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="0"/>
+        <v>"Colima" = "06",</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>264</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>7</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="0"/>
+        <v>"Chiapas" = "07",</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="0"/>
+        <v>"Chihuahua" = "08",</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>267</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad de México" = "09",</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>269</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="3">
+        <v>10</v>
+      </c>
+      <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="0"/>
+        <v>"Durango" = "10",</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>270</v>
+      </c>
+      <c r="C12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>270</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="3">
+        <v>11</v>
+      </c>
+      <c r="J12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="0"/>
+        <v>"Guanajuato" = "11",</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" t="s">
+        <v>273</v>
+      </c>
+      <c r="E13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" t="s">
+        <v>272</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="3">
+        <v>12</v>
+      </c>
+      <c r="J13" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="0"/>
+        <v>"Guerrero" = "12",</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" t="s">
+        <v>274</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="I14" s="3">
+        <v>13</v>
+      </c>
+      <c r="J14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="0"/>
+        <v>"Hidalgo" = "13",</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" t="s">
+        <v>277</v>
+      </c>
+      <c r="E15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" t="s">
+        <v>276</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I15" s="3">
+        <v>14</v>
+      </c>
+      <c r="J15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="0"/>
+        <v>"Jalisco" = "14",</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="3">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="0"/>
+        <v>"México" = "15",</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>279</v>
+      </c>
+      <c r="C17" t="s">
+        <v>280</v>
+      </c>
+      <c r="E17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F17" t="s">
+        <v>279</v>
+      </c>
+      <c r="G17" t="s">
+        <v>50</v>
+      </c>
+      <c r="I17" s="3">
+        <v>16</v>
+      </c>
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="0"/>
+        <v>"Michoacán de Ocampo" = "16",</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>281</v>
+      </c>
+      <c r="C18" t="s">
+        <v>282</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G18" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="3">
+        <v>17</v>
+      </c>
+      <c r="J18" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="0"/>
+        <v>"Morelos" = "17",</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" t="s">
+        <v>284</v>
+      </c>
+      <c r="E19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G19" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="3">
+        <v>18</v>
+      </c>
+      <c r="J19" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="0"/>
+        <v>"Nayarit" = "18",</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>285</v>
+      </c>
+      <c r="C20" t="s">
+        <v>286</v>
+      </c>
+      <c r="E20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" t="s">
+        <v>285</v>
+      </c>
+      <c r="G20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="3">
+        <v>19</v>
+      </c>
+      <c r="J20" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="0"/>
+        <v>"Nuevo León" = "19",</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>287</v>
+      </c>
+      <c r="E21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="I21" s="3">
+        <v>20</v>
+      </c>
+      <c r="J21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="0"/>
+        <v>"Oaxaca" = "20",</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" t="s">
+        <v>288</v>
+      </c>
+      <c r="E22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" t="s">
+        <v>50</v>
+      </c>
+      <c r="I22" s="3">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="0"/>
+        <v>"Puebla" = "21",</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>289</v>
+      </c>
+      <c r="E23" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" t="s">
+        <v>50</v>
+      </c>
+      <c r="I23" s="3">
+        <v>22</v>
+      </c>
+      <c r="J23" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="0"/>
+        <v>"Querétaro" = "22",</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>290</v>
+      </c>
+      <c r="C24" t="s">
+        <v>291</v>
+      </c>
+      <c r="E24" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="3">
+        <v>23</v>
+      </c>
+      <c r="J24" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="0"/>
+        <v>"Quintana Roo" = "23",</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>292</v>
+      </c>
+      <c r="E25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" t="s">
+        <v>50</v>
+      </c>
+      <c r="I25" s="3">
+        <v>24</v>
+      </c>
+      <c r="J25" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="0"/>
+        <v>"San Luis Potosí" = "24",</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" t="s">
+        <v>293</v>
+      </c>
+      <c r="G26" t="s">
+        <v>50</v>
+      </c>
+      <c r="I26" s="3">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="0"/>
+        <v>"Sinaloa" = "25",</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>295</v>
+      </c>
+      <c r="C27" t="s">
+        <v>296</v>
+      </c>
+      <c r="E27" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" t="s">
+        <v>295</v>
+      </c>
+      <c r="G27" t="s">
+        <v>50</v>
+      </c>
+      <c r="I27" s="3">
+        <v>26</v>
+      </c>
+      <c r="J27" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="0"/>
+        <v>"Sonora" = "26",</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C28" t="s">
+        <v>298</v>
+      </c>
+      <c r="E28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" t="s">
+        <v>297</v>
+      </c>
+      <c r="G28" t="s">
+        <v>50</v>
+      </c>
+      <c r="I28" s="3">
+        <v>27</v>
+      </c>
+      <c r="J28" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tabasco" = "27",</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
+      <c r="B29" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" t="s">
+        <v>300</v>
+      </c>
+      <c r="E29" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" t="s">
+        <v>50</v>
+      </c>
+      <c r="I29" s="3">
+        <v>28</v>
+      </c>
+      <c r="J29" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tamaulipas" = "28",</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>301</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" t="s">
+        <v>50</v>
+      </c>
+      <c r="I30" s="3">
+        <v>29</v>
+      </c>
+      <c r="J30" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tlaxcala" = "29",</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>302</v>
+      </c>
+      <c r="C31" t="s">
+        <v>303</v>
+      </c>
+      <c r="E31" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" t="s">
+        <v>302</v>
+      </c>
+      <c r="G31" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31" s="3">
+        <v>30</v>
+      </c>
+      <c r="J31" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="0"/>
+        <v>"Veracruz de Ignacio de la Llave" = "30",</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" t="s">
+        <v>305</v>
+      </c>
+      <c r="E32" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" t="s">
+        <v>304</v>
+      </c>
+      <c r="G32" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="3">
+        <v>31</v>
+      </c>
+      <c r="J32" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="0"/>
+        <v>"Yucatán" = "31",</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" t="s">
+        <v>306</v>
+      </c>
+      <c r="E33" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I33" s="3">
+        <v>32</v>
+      </c>
+      <c r="J33" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="0"/>
+        <v>"Zacatecas" = "32",</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71808CC9-5828-45E9-AED1-198BB387484A}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="str">
+        <f>_xlfn.CONCAT(A1:D1)</f>
+        <v xml:space="preserve"> tp = "Participación ",</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="str">
+        <f t="shared" ref="F2:F11" si="0">_xlfn.CONCAT(A2:D2)</f>
+        <v xml:space="preserve"> td = "Desocupación ",</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>310</v>
+      </c>
+      <c r="B3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> topd = "Ocupación parcial y desocupación ",</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> tpg = "Presión general ",</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> tta = "Trabajo asalariado ",</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> tsub = "Subocupación ",</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> tcco = "Condiciones críticas de ocupación ",</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" t="s">
+        <v>326</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> til1 = "Informalidad laboral 1 ",</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> tosi1 = "Ocupación en el sector informal 1 ",</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> til2 = "Informalidad laboral 2 ",</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" t="s">
+        <v>318</v>
+      </c>
+      <c r="C11" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> tosi2 = "Ocupación en el sector informal 2 ",</v>
       </c>
     </row>
   </sheetData>
@@ -979,7 +3099,7 @@
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
@@ -995,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1004,15 +3124,15 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1023,7 +3143,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -1031,8 +3151,9 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" t="s">
-        <v>68</v>
+      <c r="G3" t="str">
+        <f>_xlfn.CONCAT(A3:E3)</f>
+        <v xml:space="preserve">"sdem", "tp", "sex", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1043,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -1051,8 +3172,9 @@
       <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
-        <v>69</v>
+      <c r="G4" t="str">
+        <f t="shared" ref="G4:G35" si="0">_xlfn.CONCAT(A4:E4)</f>
+        <v xml:space="preserve">"sdem", "td", "sex", "clase2 == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1063,16 +3185,17 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="G5" t="s">
-        <v>70</v>
+      <c r="G5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "topd", "sex", "clase2 == 2 | dur9c == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1080,19 +3203,20 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="G6" t="s">
-        <v>71</v>
+      <c r="G6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tpg", "sex", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1100,19 +3224,20 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>72</v>
+      <c r="G7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tta", "sex", "remune2c == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1120,19 +3245,20 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>73</v>
+        <v>14</v>
+      </c>
+      <c r="G8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tsub", "sex", "sub_o == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1140,19 +3266,20 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>74</v>
+        <v>14</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tcco", "sex", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1160,19 +3287,20 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>75</v>
+        <v>14</v>
+      </c>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "til1", "sex", "emp_ppal == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1180,19 +3308,20 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>76</v>
+        <v>14</v>
+      </c>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tosi1", "sex", "tue2 == 5", "clase2 == 1", </v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1200,19 +3329,20 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" t="s">
-        <v>77</v>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "til2", "sex", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1220,19 +3350,20 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" t="s">
-        <v>78</v>
+        <v>24</v>
+      </c>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tosi2", "sex", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1243,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -1251,8 +3382,9 @@
       <c r="E14" t="s">
         <v>6</v>
       </c>
-      <c r="G14" t="s">
-        <v>79</v>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tp", "cve_ent", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1263,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
@@ -1271,8 +3403,9 @@
       <c r="E15" t="s">
         <v>9</v>
       </c>
-      <c r="G15" t="s">
-        <v>80</v>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "td", "cve_ent", "clase2 == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1283,16 +3416,17 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
       </c>
-      <c r="G16" t="s">
-        <v>81</v>
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "topd", "cve_ent", "clase2 == 2 | dur9c == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1300,19 +3434,20 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" t="s">
         <v>30</v>
-      </c>
-      <c r="D17" t="s">
-        <v>32</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
-      <c r="G17" t="s">
-        <v>82</v>
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tpg", "cve_ent", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1320,19 +3455,20 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" t="s">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" t="s">
-        <v>83</v>
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tta", "cve_ent", "remune2c == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1340,19 +3476,20 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" t="s">
-        <v>84</v>
+        <v>14</v>
+      </c>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tsub", "cve_ent", "sub_o == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1360,19 +3497,20 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s">
-        <v>85</v>
+        <v>14</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tcco", "cve_ent", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1380,19 +3518,20 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" t="s">
-        <v>86</v>
+        <v>14</v>
+      </c>
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "til1", "cve_ent", "emp_ppal == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1400,19 +3539,20 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" t="s">
-        <v>87</v>
+        <v>14</v>
+      </c>
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tosi1", "cve_ent", "tue2 == 5", "clase2 == 1", </v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1420,19 +3560,20 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
         <v>24</v>
       </c>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" t="s">
-        <v>88</v>
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "til2", "cve_ent", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1440,30 +3581,31 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" t="s">
-        <v>89</v>
+        <v>24</v>
+      </c>
+      <c r="G24" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "tosi2", "cve_ent", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
@@ -1471,19 +3613,20 @@
       <c r="E25" t="s">
         <v>6</v>
       </c>
-      <c r="G25" t="s">
-        <v>90</v>
+      <c r="G25" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tp", "cd_a", "clase1 == 1", "eda &gt;= 15 &amp; eda &lt;= 98", </v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s">
         <v>7</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
@@ -1491,188 +3634,198 @@
       <c r="E26" t="s">
         <v>9</v>
       </c>
-      <c r="G26" t="s">
-        <v>91</v>
+      <c r="G26" t="str">
+        <f>_xlfn.CONCAT(A26:E26)</f>
+        <v xml:space="preserve">"sdem_cd", "td", "cd_a", "clase2 == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
-      <c r="G27" t="s">
-        <v>92</v>
+      <c r="G27" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "topd", "cd_a", "clase2 == 2 | dur9c == 2", "clase1 == 1", </v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
-      <c r="G28" t="s">
-        <v>93</v>
+      <c r="G28" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tpg", "cd_a", "clase2 == 2 | tpg_p8a == 1", "clase1 == 1", </v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" t="s">
         <v>14</v>
       </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>94</v>
+      <c r="G29" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tta", "cd_a", "remune2c == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" t="s">
-        <v>95</v>
+        <v>14</v>
+      </c>
+      <c r="G30" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tsub", "cd_a", "sub_o == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31" t="s">
-        <v>96</v>
+        <v>14</v>
+      </c>
+      <c r="G31" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tcco", "cd_a", "tcco == 1 | tcco == 2 | tcco == 3", "clase2 == 1", </v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" t="s">
-        <v>97</v>
+        <v>14</v>
+      </c>
+      <c r="G32" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "til1", "cd_a", "emp_ppal == 1", "clase2 == 1", </v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" t="s">
-        <v>98</v>
+        <v>14</v>
+      </c>
+      <c r="G33" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tosi1", "cd_a", "tue2 == 5", "clase2 == 1", </v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
         <v>24</v>
       </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" t="s">
-        <v>99</v>
+      <c r="G34" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "til2", "cd_a", "emp_ppal == 1 &amp; ambito1 != 1", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" t="s">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "tosi2", "cd_a", "tue2 == 5", "clase2 == 1 &amp; ambito1 != 1", </v>
       </c>
     </row>
   </sheetData>
@@ -1682,7 +3835,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F06F828-FA51-447B-9701-6F078342E1B6}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
@@ -1694,21 +3847,21 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1716,13 +3869,14 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>49</v>
+      <c r="E3" t="str">
+        <f>_xlfn.CONCAT(A3:C3)</f>
+        <v xml:space="preserve">"sdem", "pea", "clase1 == 1", </v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1730,13 +3884,14 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" ref="E4:E14" si="0">_xlfn.CONCAT(A4:C4)</f>
+        <v xml:space="preserve">"sdem", "pnea", "clase1 == 2", </v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1744,13 +3899,14 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
+        <v>14</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "ocupada", "clase2 == 1", </v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1758,13 +3914,14 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="E6" t="s">
-        <v>52</v>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "desocupada", "clase2 == 2", </v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1772,13 +3929,14 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "disponible", "clase2 == 3", </v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -1786,13 +3944,104 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem", "no disponible", "clase2 == 4", </v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "pea", "clase1 == 1", </v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
-        <v>54</v>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "pnea", "clase1 == 2", </v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "ocupada", "clase2 == 1", </v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "desocupada", "clase2 == 2", </v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "disponible", "clase2 == 3", </v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">"sdem_cd", "no disponible", "clase2 == 4", </v>
       </c>
     </row>
   </sheetData>
@@ -1814,13 +4063,13 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>37</v>
       </c>
       <c r="F1" t="str">
         <f>_xlfn.CONCAT(A1:D1)</f>
@@ -1829,7 +4078,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F2" t="str">
         <f t="shared" ref="F2" si="0">_xlfn.CONCAT(A2:D2)</f>
@@ -1841,16 +4090,17 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
-        <v>101</v>
+      <c r="F3" t="str">
+        <f>_xlfn.CONCAT(A3:D3)</f>
+        <v xml:space="preserve">"sdem", "pea", "sex", "clase1 == 1", </v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1858,16 +4108,17 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" t="s">
-        <v>102</v>
+        <v>45</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" ref="F4:F20" si="1">_xlfn.CONCAT(A4:D4)</f>
+        <v xml:space="preserve">"sdem", "pnea", "sex", "clase1 == 2", </v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1875,16 +4126,17 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>103</v>
+        <v>14</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "ocupada", "sex", "clase2 == 1", </v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1892,16 +4144,17 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
-      <c r="F6" t="s">
-        <v>104</v>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "desocupada", "sex", "clase2 == 2", </v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -1909,16 +4162,17 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" t="s">
-        <v>105</v>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "disponible", "sex", "clase2 == 3", </v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1926,16 +4180,17 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" t="s">
-        <v>106</v>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "no disponible", "sex", "clase2 == 4", </v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -1943,16 +4198,17 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="F9" t="s">
-        <v>107</v>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "pea", "cve_ent", "clase1 == 1", </v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1960,16 +4216,17 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" t="s">
-        <v>108</v>
+        <v>45</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "pnea", "cve_ent", "clase1 == 2", </v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1977,16 +4234,17 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" t="s">
-        <v>109</v>
+        <v>14</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "ocupada", "cve_ent", "clase2 == 1", </v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1994,16 +4252,17 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
         <v>8</v>
       </c>
-      <c r="F12" t="s">
-        <v>110</v>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "desocupada", "cve_ent", "clase2 == 2", </v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -2011,16 +4270,17 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>111</v>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "disponible", "cve_ent", "clase2 == 3", </v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2028,121 +4288,4054 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" t="s">
-        <v>112</v>
+      <c r="F14" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem", "no disponible", "cve_ent", "clase2 == 4", </v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
       </c>
-      <c r="F15" t="s">
-        <v>113</v>
+      <c r="F15" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem_cd", "pea", "cd_a", "clase1 == 1", </v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" t="s">
-        <v>114</v>
+        <v>45</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem_cd", "pnea", "cd_a", "clase1 == 2", </v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" t="s">
-        <v>115</v>
+        <v>14</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem_cd", "ocupada", "cd_a", "clase2 == 1", </v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
         <v>8</v>
       </c>
-      <c r="F18" t="s">
-        <v>116</v>
+      <c r="F18" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem_cd", "desocupada", "cd_a", "clase2 == 2", </v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
         <v>41</v>
       </c>
-      <c r="C19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>117</v>
+      <c r="F19" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem_cd", "disponible", "cd_a", "clase2 == 3", </v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" t="s">
-        <v>118</v>
+      <c r="F20" t="str">
+        <f t="shared" si="1"/>
+        <v xml:space="preserve">"sdem_cd", "no disponible", "cd_a", "clase2 == 4", </v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB2B612D-C710-4F8A-AD97-41B18F386F63}">
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" t="str">
+        <f t="shared" ref="F2:F46" si="0">_xlfn.CONCAT(A2:E2)</f>
+        <v>"México" = "1",</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" si="0"/>
+        <v>"Guadalajara" = "2",</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="0"/>
+        <v>"Monterrey" = "3",</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="0"/>
+        <v>"Puebla" = "4",</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>"León" = "5",</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>"Torreón" = "6",</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>"San Luis Potosí" = "7",</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>"Mérida" = "8",</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="0"/>
+        <v>"Chihuahua" = "9",</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tampico" = "10",</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="0"/>
+        <v>"Veracruz" = "12",</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13">
+        <v>13</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="0"/>
+        <v>"Acapulco" = "13",</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="0"/>
+        <v>"Aguascalientes" = "14",</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="0"/>
+        <v>"Morelia" = "15",</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="0"/>
+        <v>"Toluca" = "16",</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17">
+        <v>17</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="str">
+        <f t="shared" si="0"/>
+        <v>"Saltillo" = "17",</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>18</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" t="str">
+        <f t="shared" si="0"/>
+        <v>"Villahermosa" = "18",</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19">
+        <v>19</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tuxtla Gutiérrez" = "19",</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>20</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad Juárez" = "20",</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21">
+        <v>21</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tijuana" = "21",</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" t="str">
+        <f t="shared" si="0"/>
+        <v>"Culiacán" = "24",</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23">
+        <v>25</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="0"/>
+        <v>"Hermosillo" = "25",</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>26</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24" t="str">
+        <f t="shared" si="0"/>
+        <v>"Durango" = "26",</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>27</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tepic" = "27",</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26">
+        <v>28</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" t="str">
+        <f t="shared" si="0"/>
+        <v>"Campeche" = "28",</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27">
+        <v>29</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" t="str">
+        <f t="shared" si="0"/>
+        <v>"Cuernavaca" = "29",</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28">
+        <v>30</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" t="str">
+        <f t="shared" si="0"/>
+        <v>"Coatzacoalcos" = "30",</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29">
+        <v>31</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" t="str">
+        <f t="shared" si="0"/>
+        <v>"Oaxaca" = "31",</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30">
+        <v>32</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" t="str">
+        <f t="shared" si="0"/>
+        <v>"Zacatecas" = "32",</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31">
+        <v>33</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" t="str">
+        <f t="shared" si="0"/>
+        <v>"Colima" = "33",</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32">
+        <v>36</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" t="str">
+        <f t="shared" si="0"/>
+        <v>"Querétaro" = "36",</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33">
+        <v>39</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tlaxcala" = "39",</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34">
+        <v>40</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F34" t="str">
+        <f t="shared" si="0"/>
+        <v>"La Paz" = "40",</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35">
+        <v>41</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F35" t="str">
+        <f t="shared" si="0"/>
+        <v>"Cancún" = "41",</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36">
+        <v>42</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F36" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad del Carmen" = "42",</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>43</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" t="str">
+        <f t="shared" si="0"/>
+        <v>"Pachuca" = "43",</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38">
+        <v>44</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F38" t="str">
+        <f t="shared" si="0"/>
+        <v>"Mexicali" = "44",</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39">
+        <v>46</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F39" t="str">
+        <f t="shared" si="0"/>
+        <v>"Reynosa" = "46",</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40">
+        <v>52</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F40" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tapachula" = "52",</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41">
+        <v>81</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="str">
+        <f t="shared" si="0"/>
+        <v>"Áreas rurales hasta 86" = "81",</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42">
+        <v>82</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F42" t="str">
+        <f t="shared" si="0"/>
+        <v>"Áreas rurales o comp. urb." = "82",</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43">
+        <v>83</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="str">
+        <f t="shared" si="0"/>
+        <v>"Áreas rurales o comp. urb." = "83",</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44">
+        <v>84</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" t="str">
+        <f t="shared" si="0"/>
+        <v>"Áreas rurales o comp. urb." = "84",</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45">
+        <v>85</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F45" t="str">
+        <f t="shared" si="0"/>
+        <v>"Áreas rurales o comp. urb." = "85",</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46">
+        <v>86</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F46" t="str">
+        <f t="shared" si="0"/>
+        <v>"Áreas rurales o comp. urb." = "86",</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25448D16-AE2B-4665-BF88-AAEFB611E3A4}">
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.21875" customWidth="1"/>
+    <col min="9" max="9" width="46.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I46" si="0">_xlfn.CONCAT(C2:G2)</f>
+        <v>"Ciudad de México (CDMX y Méx.)" = "1",</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>"Guadalajara (Jal.)" = "2",</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="1"/>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>"Monterrey (N. L.)" = "3",</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>"Puebla (Pue.)" = "4",</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>"León (Gto.)" = "5",</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>"Torreón - La Laguna (Coah. y Dgo.)" = "6",</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>"San Luis Potosí (S. L. P.)" = "7",</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>"Mérida (Yuc.)" = "8",</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>"Chihuahua (Chih.)" = "9",</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>124</v>
+      </c>
+      <c r="E11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="1"/>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tampico (Tamps. y Ver.)" = "10",</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="1"/>
+      <c r="I12" t="str">
+        <f t="shared" si="0"/>
+        <v>"Veracruz (Ver.)" = "12",</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" t="str">
+        <f t="shared" si="0"/>
+        <v>"Acapulco de Juárez (Gro.)" = "13",</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" t="str">
+        <f t="shared" si="0"/>
+        <v>"Aguascalientes (Ags.)" = "14",</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15">
+        <v>15</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" t="str">
+        <f t="shared" si="0"/>
+        <v>"Morelia (Mich.)" = "15",</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="1"/>
+      <c r="I16" t="str">
+        <f t="shared" si="0"/>
+        <v>"Toluca (Méx.)" = "16",</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>17</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v>"Saltillo (Coah.)" = "17",</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <v>18</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v>"Villahermosa (Tab.)" = "18",</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>19</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tuxtla Gutiérrez (Chis.)" = "19",</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="1"/>
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad Juárez (Chih.)" = "20",</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21">
+        <v>21</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tijuana (B. C.)" = "21",</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22">
+        <v>24</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" t="str">
+        <f t="shared" si="0"/>
+        <v>"Culiacán (Sin.)" = "24",</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23">
+        <v>25</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v>"Hermosillo (Son.)" = "25",</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24">
+        <v>26</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v>"Durango (Dgo.)" = "26",</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>27</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tepic (Nay.)" = "27",</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <v>28</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" t="str">
+        <f t="shared" si="0"/>
+        <v>"Campeche (Camp.)" = "28",</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" t="s">
+        <v>50</v>
+      </c>
+      <c r="F27">
+        <v>29</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="1"/>
+      <c r="I27" t="str">
+        <f t="shared" si="0"/>
+        <v>"Cuernavaca (Mor.)" = "29",</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28">
+        <v>30</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" t="str">
+        <f t="shared" si="0"/>
+        <v>"Coatzacoalcos (Ver.)" = "30",</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F29">
+        <v>31</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" t="str">
+        <f t="shared" si="0"/>
+        <v>"Oaxaca (Oax.)" = "31",</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="I30" t="str">
+        <f t="shared" si="0"/>
+        <v>"Zacatecas (Zac.)" = "32",</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31">
+        <v>33</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" t="str">
+        <f t="shared" si="0"/>
+        <v>"Colima (Col.)" = "33",</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32">
+        <v>36</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="I32" t="str">
+        <f t="shared" si="0"/>
+        <v>"Querétaro (Qro.)" = "36",</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33">
+        <v>39</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="1"/>
+      <c r="I33" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tlaxcala (Tlax.)" = "39",</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34">
+        <v>40</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" t="str">
+        <f t="shared" si="0"/>
+        <v>"La Paz (B. C. S.)" = "40",</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35">
+        <v>41</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" s="1"/>
+      <c r="I35" t="str">
+        <f t="shared" si="0"/>
+        <v>"Cancún (Q. Roo)" = "41",</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E36" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36">
+        <v>42</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" s="1"/>
+      <c r="I36" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad del Carmen (Camp.)" = "42",</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37">
+        <v>43</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" s="1"/>
+      <c r="I37" t="str">
+        <f t="shared" si="0"/>
+        <v>"Pachuca (Hgo.)" = "43",</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38">
+        <v>44</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38" t="str">
+        <f t="shared" si="0"/>
+        <v>"Mexicali (B. C.)" = "44",</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D39" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39">
+        <v>46</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="I39" t="str">
+        <f t="shared" si="0"/>
+        <v>"Reynosa (Tamps.)" = "46",</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40">
+        <v>52</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="I40" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tapachula (Chis.)" = "52",</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E41" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41">
+        <v>81</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" s="1"/>
+      <c r="I41" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E42" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42">
+        <v>82</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" s="1"/>
+      <c r="I42" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E43" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43">
+        <v>83</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" s="1"/>
+      <c r="I43" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44">
+        <v>84</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H44" s="1"/>
+      <c r="I44" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E45" t="s">
+        <v>50</v>
+      </c>
+      <c r="F45">
+        <v>85</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H45" s="1"/>
+      <c r="I45" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E46" t="s">
+        <v>50</v>
+      </c>
+      <c r="F46">
+        <v>86</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H46" s="1"/>
+      <c r="I46" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD0D82B6-A6B9-4A78-AF55-F50CF8CD3D25}">
+  <dimension ref="A1:A40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A42" xr:uid="{C332A697-1B6D-4555-81C1-DDE296D1C38B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A42">
+      <sortCondition ref="A1:A42"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17594B1E-31E2-4D28-A1BC-99357E3BD842}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A40" xr:uid="{3C244326-C71C-4125-913B-01D858D979C4}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A40">
+      <sortCondition ref="A1:A40"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B09E9B5F-18F4-42F0-965E-79A38F43D5E0}">
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" t="s">
+        <v>251</v>
+      </c>
+      <c r="E1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I1" t="str">
+        <f>_xlfn.CONCAT(A1:G1)</f>
+        <v>~cd_cuadro, ABREV~cve_ent,</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>335</v>
+      </c>
+      <c r="I2" t="str">
+        <f t="shared" ref="I2:I41" si="0">_xlfn.CONCAT(A2:G2)</f>
+        <v># ------</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" si="0"/>
+        <v>"Aguascalientes (Ags.)", 1,</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" t="s">
+        <v>332</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="0"/>
+        <v>"Mexicali (B. C.)", 2,</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" t="s">
+        <v>331</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" t="s">
+        <v>332</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tijuana (B. C.)", 2,</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="0"/>
+        <v>"La Paz (B. C. S.)", 3,</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>332</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="0"/>
+        <v>"Campeche (Camp.)", 4,</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E8" t="s">
+        <v>331</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>332</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad del Carmen (Camp.)", 4,</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" t="s">
+        <v>330</v>
+      </c>
+      <c r="D9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="0"/>
+        <v>"Torreón - La Laguna (Coah. y Dgo.)", 5,</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E10" t="s">
+        <v>331</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>332</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="0"/>
+        <v>"Saltillo (Coah.)", 5,</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" t="s">
+        <v>331</v>
+      </c>
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11" t="s">
+        <v>332</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="0"/>
+        <v>"Colima (Col.)", 6,</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12" t="s">
+        <v>331</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s">
+        <v>332</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tapachula (Chis.)", 7,</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" t="s">
+        <v>331</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s">
+        <v>332</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tuxtla Gutiérrez (Chis.)", 7,</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" t="s">
+        <v>330</v>
+      </c>
+      <c r="D14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" t="s">
+        <v>331</v>
+      </c>
+      <c r="F14">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>332</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="0"/>
+        <v>"Chihuahua (Chih.)", 8,</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" t="s">
+        <v>330</v>
+      </c>
+      <c r="D15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E15" t="s">
+        <v>331</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>332</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad Juárez (Chih.)", 8,</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C16" t="s">
+        <v>330</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>332</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="0"/>
+        <v>"Ciudad de México (CDMX y Méx.)", 9,</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C17" t="s">
+        <v>330</v>
+      </c>
+      <c r="D17" t="s">
+        <v>199</v>
+      </c>
+      <c r="E17" t="s">
+        <v>331</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>332</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="0"/>
+        <v>"Durango (Dgo.)", 10,</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" t="s">
+        <v>330</v>
+      </c>
+      <c r="D18" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18">
+        <v>11</v>
+      </c>
+      <c r="G18" t="s">
+        <v>332</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="0"/>
+        <v>"León (Gto.)", 11,</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" t="s">
+        <v>330</v>
+      </c>
+      <c r="D19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" t="s">
+        <v>331</v>
+      </c>
+      <c r="F19">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>332</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="0"/>
+        <v>"Acapulco de Juárez (Gro.)", 12,</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20" t="s">
+        <v>330</v>
+      </c>
+      <c r="D20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E20" t="s">
+        <v>331</v>
+      </c>
+      <c r="F20">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
+        <v>332</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="0"/>
+        <v>"Pachuca (Hgo.)", 13,</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" t="s">
+        <v>330</v>
+      </c>
+      <c r="D21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E21" t="s">
+        <v>331</v>
+      </c>
+      <c r="F21">
+        <v>14</v>
+      </c>
+      <c r="G21" t="s">
+        <v>332</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="0"/>
+        <v>"Guadalajara (Jal.)", 14,</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" t="s">
+        <v>330</v>
+      </c>
+      <c r="D22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" t="s">
+        <v>331</v>
+      </c>
+      <c r="F22">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s">
+        <v>332</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="0"/>
+        <v>"Toluca (Méx.)", 15,</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" t="s">
+        <v>330</v>
+      </c>
+      <c r="D23" t="s">
+        <v>217</v>
+      </c>
+      <c r="E23" t="s">
+        <v>331</v>
+      </c>
+      <c r="F23">
+        <v>16</v>
+      </c>
+      <c r="G23" t="s">
+        <v>332</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="0"/>
+        <v>"Morelia (Mich.)", 16,</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" t="s">
+        <v>330</v>
+      </c>
+      <c r="D24" t="s">
+        <v>195</v>
+      </c>
+      <c r="E24" t="s">
+        <v>331</v>
+      </c>
+      <c r="F24">
+        <v>17</v>
+      </c>
+      <c r="G24" t="s">
+        <v>332</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="0"/>
+        <v>"Cuernavaca (Mor.)", 17,</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" t="s">
+        <v>330</v>
+      </c>
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" t="s">
+        <v>331</v>
+      </c>
+      <c r="F25">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>332</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tepic (Nay.)", 18,</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>214</v>
+      </c>
+      <c r="C26" t="s">
+        <v>330</v>
+      </c>
+      <c r="D26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E26" t="s">
+        <v>331</v>
+      </c>
+      <c r="F26">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s">
+        <v>332</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="0"/>
+        <v>"Monterrey (N. L.)", 19,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>218</v>
+      </c>
+      <c r="C27" t="s">
+        <v>330</v>
+      </c>
+      <c r="D27" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" t="s">
+        <v>331</v>
+      </c>
+      <c r="F27">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>332</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="0"/>
+        <v>"Oaxaca (Oax.)", 20,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" t="s">
+        <v>330</v>
+      </c>
+      <c r="D28" t="s">
+        <v>223</v>
+      </c>
+      <c r="E28" t="s">
+        <v>331</v>
+      </c>
+      <c r="F28">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>332</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="0"/>
+        <v>"Puebla (Pue.)", 21,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" t="s">
+        <v>330</v>
+      </c>
+      <c r="D29" t="s">
+        <v>225</v>
+      </c>
+      <c r="E29" t="s">
+        <v>331</v>
+      </c>
+      <c r="F29">
+        <v>22</v>
+      </c>
+      <c r="G29" t="s">
+        <v>332</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="0"/>
+        <v>"Querétaro (Qro.)", 22,</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" t="s">
+        <v>330</v>
+      </c>
+      <c r="D30" t="s">
+        <v>185</v>
+      </c>
+      <c r="E30" t="s">
+        <v>331</v>
+      </c>
+      <c r="F30">
+        <v>23</v>
+      </c>
+      <c r="G30" t="s">
+        <v>332</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="0"/>
+        <v>"Cancún (Q. Roo)", 23,</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" t="s">
+        <v>330</v>
+      </c>
+      <c r="D31" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" t="s">
+        <v>331</v>
+      </c>
+      <c r="F31">
+        <v>24</v>
+      </c>
+      <c r="G31" t="s">
+        <v>332</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="0"/>
+        <v>"San Luis Potosí (S. L. P.)", 24,</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" t="s">
+        <v>330</v>
+      </c>
+      <c r="D32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32" t="s">
+        <v>331</v>
+      </c>
+      <c r="F32">
+        <v>25</v>
+      </c>
+      <c r="G32" t="s">
+        <v>332</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="0"/>
+        <v>"Culiacán (Sin.)", 25,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D33" t="s">
+        <v>203</v>
+      </c>
+      <c r="E33" t="s">
+        <v>331</v>
+      </c>
+      <c r="F33">
+        <v>26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>332</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="0"/>
+        <v>"Hermosillo (Son.)", 26,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>247</v>
+      </c>
+      <c r="C34" t="s">
+        <v>330</v>
+      </c>
+      <c r="D34" t="s">
+        <v>248</v>
+      </c>
+      <c r="E34" t="s">
+        <v>331</v>
+      </c>
+      <c r="F34">
+        <v>27</v>
+      </c>
+      <c r="G34" t="s">
+        <v>332</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="0"/>
+        <v>"Villahermosa (Tab.)", 27,</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" t="s">
+        <v>330</v>
+      </c>
+      <c r="D35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" t="s">
+        <v>331</v>
+      </c>
+      <c r="F35">
+        <v>28</v>
+      </c>
+      <c r="G35" t="s">
+        <v>332</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tampico (Tamps. y Ver.)", 28,</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" t="s">
+        <v>331</v>
+      </c>
+      <c r="F36">
+        <v>28</v>
+      </c>
+      <c r="G36" t="s">
+        <v>332</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="0"/>
+        <v>"Reynosa (Tamps.)", 28,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>239</v>
+      </c>
+      <c r="C37" t="s">
+        <v>330</v>
+      </c>
+      <c r="D37" t="s">
+        <v>240</v>
+      </c>
+      <c r="E37" t="s">
+        <v>331</v>
+      </c>
+      <c r="F37">
+        <v>29</v>
+      </c>
+      <c r="G37" t="s">
+        <v>332</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="0"/>
+        <v>"Tlaxcala (Tlax.)", 29,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" t="s">
+        <v>330</v>
+      </c>
+      <c r="D38" t="s">
+        <v>191</v>
+      </c>
+      <c r="E38" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>332</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="0"/>
+        <v>"Coatzacoalcos (Ver.)", 30,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>246</v>
+      </c>
+      <c r="C39" t="s">
+        <v>330</v>
+      </c>
+      <c r="D39" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" t="s">
+        <v>331</v>
+      </c>
+      <c r="F39">
+        <v>30</v>
+      </c>
+      <c r="G39" t="s">
+        <v>332</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="0"/>
+        <v>"Veracruz (Ver.)", 30,</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>208</v>
+      </c>
+      <c r="C40" t="s">
+        <v>330</v>
+      </c>
+      <c r="D40" t="s">
+        <v>209</v>
+      </c>
+      <c r="E40" t="s">
+        <v>331</v>
+      </c>
+      <c r="F40">
+        <v>31</v>
+      </c>
+      <c r="G40" t="s">
+        <v>332</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="0"/>
+        <v>"Mérida (Yuc.)", 31,</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>249</v>
+      </c>
+      <c r="C41" t="s">
+        <v>330</v>
+      </c>
+      <c r="D41" t="s">
+        <v>250</v>
+      </c>
+      <c r="E41" t="s">
+        <v>331</v>
+      </c>
+      <c r="F41">
+        <v>32</v>
+      </c>
+      <c r="G41" t="s">
+        <v>332</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="0"/>
+        <v>"Zacatecas (Zac.)", 32,</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:F41" xr:uid="{B09E9B5F-18F4-42F0-965E-79A38F43D5E0}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F41">
+      <sortCondition ref="F1:F41"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>